--- a/議員データ.xlsx
+++ b/議員データ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\nobeoka-gikai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/346989c40827ea06/ドキュメント/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBC9D1B-790A-412B-8429-184B19BD81D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="13_ncr:1_{DBBC9D1B-790A-412B-8429-184B19BD81D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D7ED95-8C44-482E-BF4B-F7886C32F684}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="296">
   <si>
     <t>ID</t>
   </si>
@@ -197,9 +197,6 @@
     <t>m03</t>
   </si>
   <si>
-    <t>上杉 泰洋</t>
-  </si>
-  <si>
     <t>うえすぎ やすひろ</t>
   </si>
   <si>
@@ -283,9 +280,6 @@
     <t>m06</t>
   </si>
   <si>
-    <t>甲斐 行雄</t>
-  </si>
-  <si>
     <t>かい いくお</t>
   </si>
   <si>
@@ -304,9 +298,6 @@
     <t>m07</t>
   </si>
   <si>
-    <t>甲斐 忠篤</t>
-  </si>
-  <si>
     <t>かい ただあつ</t>
   </si>
   <si>
@@ -343,32 +334,6 @@
     <t>m10</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-      </rPr>
-      <t>河野</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-      </rPr>
-      <t>治満</t>
-    </r>
-  </si>
-  <si>
     <t>かわの はるみつ</t>
   </si>
   <si>
@@ -390,9 +355,6 @@
     <t>m12</t>
   </si>
   <si>
-    <t>後藤 司光</t>
-  </si>
-  <si>
     <t>ごとう もりみつ</t>
   </si>
   <si>
@@ -408,9 +370,6 @@
     <t>m13</t>
   </si>
   <si>
-    <t>小御門 綾</t>
-  </si>
-  <si>
     <t>こみかど あや</t>
   </si>
   <si>
@@ -471,9 +430,6 @@
     <t>m17</t>
   </si>
   <si>
-    <t>長友 幸子</t>
-  </si>
-  <si>
     <t>ながとも さちこ</t>
   </si>
   <si>
@@ -489,9 +445,6 @@
     <t>m18</t>
   </si>
   <si>
-    <t>早瀬 賢一</t>
-  </si>
-  <si>
     <t>はやせ けんいち</t>
   </si>
   <si>
@@ -585,9 +538,6 @@
     <t>m25</t>
   </si>
   <si>
-    <t>山本 珠美</t>
-  </si>
-  <si>
     <t>やまもと あけみ</t>
   </si>
   <si>
@@ -595,9 +545,6 @@
   </si>
   <si>
     <t>m26</t>
-  </si>
-  <si>
-    <t>吉田 茂仁</t>
   </si>
   <si>
     <t>よしだ しげひと</t>
@@ -1006,12 +953,391 @@
     <t>https://www.city.nobeoka.miyazaki.jp/site/gikai/1394.html</t>
     <phoneticPr fontId="5"/>
   </si>
+  <si>
+    <t>https://www.instagram.com/masayuki_inada/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://masayuki-ricefield.hatenablog.jp/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/satoshi.inohana/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/satoshi.inohana/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>上杉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>泰洋</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100039255065122#</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100007160117141</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>甲斐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>行雄</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ikuo.kai.5/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>甲斐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>忠篤</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/p/%E7%94%B2%E6%96%90%E5%BF%A0%E7%AF%A4-100028794542251/?utm_source=chatgpt.com</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/papa.mama.marchan/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+      </rPr>
+      <t>河野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+      </rPr>
+      <t>治満</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>未確認</t>
+  </si>
+  <si>
+    <t>未確認</t>
+    <rPh sb="0" eb="3">
+      <t>ミカクニン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/100080664301633/?utm_source=chatgpt.com</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>後藤 司光</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/morimitsugoto/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://x.com/Morimitsugoto</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/morimitsu.g/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>小御門 綾</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/aya.comicado</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://lin.ee/HLXDNIS</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shiba_hiro_rosso1541/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Threads</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.threads.com/@shiba_hiro_rosso1541</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yoshiharu_nakashima/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/100083679123855/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>長友</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>幸子</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>早瀬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>賢一</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hayase_kenichi/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/kenichi.hayase.7/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ryomaeda_saw/?utm_source=chatgpt.com</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/sunandwave</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.ryomaeda.com/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>未確認</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ryo.maeda.54772/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://x.com/ryomaeda_saw</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.comicadoaya.com/?utm_source=chatgpt.com</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.komei.or.jp/km/nobeoka-ono-syoji/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.komei.or.jp/km/nobeoka-yamamoto-akemi/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://x.com/komei_yamamoto</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/579107342584087/?utm_source=chatgpt.com</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.%E3%81%BF%E3%81%AD%E3%81%A0%E5%85%8B%E6%98%8E.com/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/hironori.miyata.3/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/miyata.hironori/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>山本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>珠美</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>吉田 茂仁</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shigehitoyoshida627/?utm_source=chatgpt.com</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/shigehito.yoshida.16/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/channel/UCbD24WObkKTQnPN3eI16b4g/</t>
+    <phoneticPr fontId="5"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1098,6 +1424,17 @@
       <color theme="10"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1167,7 +1504,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1232,13 +1569,88 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="17">
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF6B7280"/>
@@ -1284,8 +1696,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MembersDataTable" displayName="MembersDataTable" ref="A1:AE27">
-  <tableColumns count="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MembersDataTable" displayName="MembersDataTable" ref="A1:AF27">
+  <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="氏名"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ふりがな"/>
@@ -1304,19 +1716,20 @@
     <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="所属委員会4"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="役職4"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="プロフィール"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="X"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Facebook"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Instagram"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="YouTube"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="LINE"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ブログ"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ホームページ"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="一般質問"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="議案への賛否"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="活動レポート"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="情報源URL"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="確認状況"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="備考"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="X" dataDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Facebook" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Instagram" dataDxfId="5"/>
+    <tableColumn id="32" xr3:uid="{AE8A63C2-B2DC-4887-A3FE-6E6E373D5B77}" name="Threads" dataDxfId="4" dataCellStyle="Normal"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="YouTube" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="LINE" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ブログ" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ホームページ" dataDxfId="0"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="一般質問" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="議案への賛否" dataDxfId="13"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="活動レポート" dataDxfId="12"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="情報源URL" dataDxfId="11"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="確認状況" dataDxfId="10"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="備考" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1483,7 +1896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF27"/>
+  <dimension ref="A1:AG27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.125" style="7" customWidth="1"/>
@@ -1504,18 +1917,20 @@
     <col min="16" max="16" width="33.875" style="7" customWidth="1"/>
     <col min="17" max="17" width="6.75" style="7" customWidth="1"/>
     <col min="18" max="18" width="14.75" style="7" customWidth="1"/>
-    <col min="19" max="24" width="11.625" style="7" customWidth="1"/>
-    <col min="25" max="25" width="14.75" style="7" customWidth="1"/>
-    <col min="26" max="26" width="11.625" style="7" customWidth="1"/>
-    <col min="27" max="28" width="14.75" style="7" customWidth="1"/>
-    <col min="29" max="29" width="11.875" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.875" style="7" customWidth="1"/>
-    <col min="31" max="31" width="5.75" style="7" customWidth="1"/>
-    <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="7"/>
+    <col min="19" max="19" width="11.625" style="7" customWidth="1"/>
+    <col min="20" max="20" width="16.125" style="7" customWidth="1"/>
+    <col min="21" max="25" width="11.625" style="7" customWidth="1"/>
+    <col min="26" max="26" width="14.75" style="29" customWidth="1"/>
+    <col min="27" max="27" width="11.625" style="7" customWidth="1"/>
+    <col min="28" max="29" width="14.75" style="7" customWidth="1"/>
+    <col min="30" max="30" width="11.875" style="7" customWidth="1"/>
+    <col min="31" max="31" width="13.875" style="7" customWidth="1"/>
+    <col min="32" max="32" width="5.75" style="7" customWidth="1"/>
+    <col min="33" max="33" width="12" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="33.950000000000003" customHeight="1">
+    <row r="1" spans="1:33" ht="33.950000000000003" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1580,40 +1995,43 @@
         <v>20</v>
       </c>
       <c r="V1" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="W1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="X1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AC1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AD1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AE1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="15" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="57">
+      <c r="AG1" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" ht="57">
       <c r="A2" s="8" t="s">
         <v>31</v>
       </c>
@@ -1656,31 +2074,31 @@
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
       <c r="R2" s="19" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="U2" s="19" t="s">
+        <v>245</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="Y2" s="19" t="s">
+        <v>246</v>
       </c>
       <c r="Z2" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA2" s="8" t="s">
         <v>41</v>
@@ -1692,14 +2110,17 @@
         <v>41</v>
       </c>
       <c r="AD2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE2" s="8"/>
-      <c r="AF2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="57">
+      <c r="AF2" s="8"/>
+      <c r="AG2" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="57">
       <c r="A3" s="8" t="s">
         <v>43</v>
       </c>
@@ -1742,31 +2163,31 @@
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="19" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T3" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="U3" s="19" t="s">
+        <v>247</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>41</v>
@@ -1778,28 +2199,31 @@
         <v>41</v>
       </c>
       <c r="AD3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE3" s="8"/>
-      <c r="AF3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="57">
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="57">
       <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="F4" s="14">
         <v>4</v>
@@ -1811,7 +2235,7 @@
         <v>36</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>38</v>
@@ -1821,38 +2245,38 @@
         <v>39</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="19" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T4" s="19" t="s">
+        <v>250</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA4" s="8" t="s">
         <v>41</v>
@@ -1864,28 +2288,31 @@
         <v>41</v>
       </c>
       <c r="AD4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE4" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE4" s="8"/>
-      <c r="AF4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" ht="57">
+      <c r="AF4" s="8"/>
+      <c r="AG4" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="57">
       <c r="A5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="F5" s="14">
         <v>4</v>
@@ -1897,10 +2324,10 @@
         <v>36</v>
       </c>
       <c r="I5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
@@ -1910,31 +2337,31 @@
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="19" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>251</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="Y5" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z5" s="19" t="s">
+        <v>284</v>
       </c>
       <c r="AA5" s="8" t="s">
         <v>41</v>
@@ -1946,22 +2373,25 @@
         <v>41</v>
       </c>
       <c r="AD5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE5" s="8"/>
-      <c r="AF5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" ht="57">
+      <c r="AF5" s="8"/>
+      <c r="AG5" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="57">
       <c r="A6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>34</v>
@@ -1979,48 +2409,48 @@
         <v>36</v>
       </c>
       <c r="I6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="19" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA6" s="8" t="s">
         <v>41</v>
@@ -2032,28 +2462,31 @@
         <v>41</v>
       </c>
       <c r="AD6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE6" s="8"/>
-      <c r="AF6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="57">
+      <c r="AF6" s="8"/>
+      <c r="AG6" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="57" customHeight="1">
       <c r="A7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="F7" s="14">
         <v>3</v>
@@ -2065,10 +2498,10 @@
         <v>36</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
@@ -2078,39 +2511,39 @@
         <v>40</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="19" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>253</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>280</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA7" s="8" t="s">
         <v>41</v>
@@ -2122,22 +2555,25 @@
         <v>41</v>
       </c>
       <c r="AD7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE7" s="8"/>
-      <c r="AF7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" ht="57">
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="57" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>254</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>34</v>
@@ -2155,10 +2591,10 @@
         <v>36</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
@@ -2170,31 +2606,31 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="19" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T8" s="19" t="s">
+        <v>255</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA8" s="8" t="s">
         <v>41</v>
@@ -2206,28 +2642,31 @@
         <v>41</v>
       </c>
       <c r="AD8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE8" s="8"/>
-      <c r="AF8" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="57">
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="57" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="F9" s="14">
         <v>4</v>
@@ -2239,14 +2678,14 @@
         <v>36</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
@@ -2254,31 +2693,31 @@
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="19" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>256</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W9" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X9" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y9" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z9" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA9" s="8" t="s">
         <v>41</v>
@@ -2290,22 +2729,25 @@
         <v>41</v>
       </c>
       <c r="AD9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE9" s="8"/>
-      <c r="AF9" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" ht="57">
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="57">
       <c r="A10" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>34</v>
@@ -2323,10 +2765,10 @@
         <v>36</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>47</v>
@@ -2335,40 +2777,40 @@
         <v>48</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
       <c r="R10" s="19" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="Y10" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="AA10" s="8" t="s">
         <v>41</v>
@@ -2380,28 +2822,31 @@
         <v>41</v>
       </c>
       <c r="AD10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE10" s="8"/>
-      <c r="AF10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="57">
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="57">
       <c r="A11" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>257</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="F11" s="14">
         <v>6</v>
@@ -2413,10 +2858,10 @@
         <v>36</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>47</v>
@@ -2426,37 +2871,37 @@
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="19" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="U11" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="V11" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W11" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="X11" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="Y11" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="Z11" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="AA11" s="8" t="s">
         <v>41</v>
@@ -2468,22 +2913,25 @@
         <v>41</v>
       </c>
       <c r="AD11" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE11" s="8"/>
-      <c r="AF11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" ht="57">
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="57">
       <c r="A12" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>34</v>
@@ -2501,10 +2949,10 @@
         <v>36</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
@@ -2514,31 +2962,31 @@
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
       <c r="R12" s="19" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T12" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>260</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W12" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="X12" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="Y12" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="Z12" s="8" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="AA12" s="8" t="s">
         <v>41</v>
@@ -2550,28 +2998,31 @@
         <v>41</v>
       </c>
       <c r="AD12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE12" s="8"/>
-      <c r="AF12" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" ht="57">
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="57">
       <c r="A13" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>99</v>
+        <v>261</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F13" s="14">
         <v>1</v>
@@ -2583,10 +3034,10 @@
         <v>36</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -2596,31 +3047,31 @@
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
       <c r="R13" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U13" s="8" t="s">
-        <v>41</v>
+        <v>230</v>
+      </c>
+      <c r="S13" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="T13" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="U13" s="19" t="s">
+        <v>262</v>
       </c>
       <c r="V13" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W13" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X13" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y13" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z13" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA13" s="8" t="s">
         <v>41</v>
@@ -2632,28 +3083,31 @@
         <v>41</v>
       </c>
       <c r="AD13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE13" s="8"/>
-      <c r="AF13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" ht="57">
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" ht="57">
       <c r="A14" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>105</v>
+        <v>265</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -2665,48 +3119,48 @@
         <v>36</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
       <c r="R14" s="19" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="S14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T14" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T14" s="19" t="s">
+        <v>266</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="X14" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="X14" s="19" t="s">
+        <v>267</v>
       </c>
       <c r="Y14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z14" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="Z14" s="19" t="s">
+        <v>283</v>
       </c>
       <c r="AA14" s="8" t="s">
         <v>41</v>
@@ -2718,22 +3172,25 @@
         <v>41</v>
       </c>
       <c r="AD14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE14" s="8"/>
-      <c r="AF14" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="57">
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" ht="57">
       <c r="A15" s="8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>34</v>
@@ -2751,14 +3208,14 @@
         <v>36</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>40</v>
@@ -2768,31 +3225,31 @@
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="19" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="S15" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V15" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="U15" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="V15" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="W15" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X15" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z15" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA15" s="8" t="s">
         <v>41</v>
@@ -2804,22 +3261,25 @@
         <v>41</v>
       </c>
       <c r="AD15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE15" s="8"/>
-      <c r="AF15" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" ht="57">
+      <c r="AF15" s="8"/>
+      <c r="AG15" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" ht="57">
       <c r="A16" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>34</v>
@@ -2837,16 +3297,16 @@
         <v>36</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -2854,31 +3314,31 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="19" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="S16" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T16" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U16" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T16" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="U16" s="19" t="s">
+        <v>271</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W16" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X16" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y16" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z16" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA16" s="8" t="s">
         <v>41</v>
@@ -2890,28 +3350,31 @@
         <v>41</v>
       </c>
       <c r="AD16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE16" s="8"/>
-      <c r="AF16" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" ht="57">
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" ht="57">
       <c r="A17" s="8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F17" s="14">
         <v>6</v>
@@ -2923,10 +3386,10 @@
         <v>36</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -2936,31 +3399,31 @@
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
       <c r="R17" s="19" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="S17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="U17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA17" s="8" t="s">
         <v>41</v>
@@ -2972,28 +3435,31 @@
         <v>41</v>
       </c>
       <c r="AD17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE17" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE17" s="8"/>
-      <c r="AF17" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" ht="57">
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" ht="57">
       <c r="A18" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>126</v>
+        <v>119</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>273</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F18" s="14">
         <v>4</v>
@@ -3005,14 +3471,14 @@
         <v>36</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
@@ -3020,31 +3486,31 @@
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="19" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="U18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA18" s="8" t="s">
         <v>41</v>
@@ -3056,28 +3522,31 @@
         <v>41</v>
       </c>
       <c r="AD18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE18" s="8"/>
-      <c r="AF18" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" ht="28.5">
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" ht="57">
       <c r="A19" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>132</v>
+        <v>124</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>274</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" s="14">
         <v>5</v>
@@ -3089,10 +3558,10 @@
         <v>36</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -3102,31 +3571,31 @@
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="20" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="S19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U19" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T19" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="U19" s="19" t="s">
+        <v>275</v>
       </c>
       <c r="V19" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W19" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X19" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y19" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z19" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA19" s="8" t="s">
         <v>41</v>
@@ -3138,28 +3607,31 @@
         <v>41</v>
       </c>
       <c r="AD19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE19" s="8"/>
-      <c r="AF19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" ht="57">
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" ht="57">
       <c r="A20" s="8" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -3171,10 +3643,10 @@
         <v>36</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8" t="s">
@@ -3186,31 +3658,31 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="19" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="S20" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="U20" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V20" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W20" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="W20" s="10" t="s">
+        <v>280</v>
       </c>
       <c r="X20" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y20" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z20" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA20" s="8" t="s">
         <v>41</v>
@@ -3222,28 +3694,31 @@
         <v>41</v>
       </c>
       <c r="AD20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE20" s="8"/>
-      <c r="AF20" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" ht="57">
+      <c r="AF20" s="8"/>
+      <c r="AG20" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" ht="57">
       <c r="A21" s="8" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F21" s="14">
         <v>7</v>
@@ -3255,48 +3730,48 @@
         <v>36</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M21" s="8"/>
       <c r="N21" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="19" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="S21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="U21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z21" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA21" s="8" t="s">
         <v>41</v>
@@ -3308,28 +3783,31 @@
         <v>41</v>
       </c>
       <c r="AD21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE21" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE21" s="8"/>
-      <c r="AF21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" ht="57">
+      <c r="AF21" s="8"/>
+      <c r="AG21" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" ht="70.5" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -3341,13 +3819,13 @@
         <v>36</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
@@ -3356,22 +3834,22 @@
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T22" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U22" s="8" t="s">
-        <v>41</v>
+        <v>239</v>
+      </c>
+      <c r="S22" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="T22" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="U22" s="19" t="s">
+        <v>277</v>
       </c>
       <c r="V22" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W22" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="W22" s="19" t="s">
+        <v>278</v>
       </c>
       <c r="X22" s="8" t="s">
         <v>41</v>
@@ -3379,8 +3857,8 @@
       <c r="Y22" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="Z22" s="8" t="s">
-        <v>41</v>
+      <c r="Z22" s="24" t="s">
+        <v>279</v>
       </c>
       <c r="AA22" s="8" t="s">
         <v>41</v>
@@ -3392,22 +3870,25 @@
         <v>41</v>
       </c>
       <c r="AD22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE22" s="8"/>
-      <c r="AF22" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" ht="57">
+      <c r="AF22" s="8"/>
+      <c r="AG22" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" ht="57">
       <c r="A23" s="8" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>34</v>
@@ -3425,10 +3906,10 @@
         <v>36</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
@@ -3438,31 +3919,31 @@
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="19" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z23" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA23" s="8" t="s">
         <v>41</v>
@@ -3474,28 +3955,31 @@
         <v>41</v>
       </c>
       <c r="AD23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE23" s="8"/>
-      <c r="AF23" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" ht="57">
+      <c r="AF23" s="8"/>
+      <c r="AG23" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" ht="85.5">
       <c r="A24" s="8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="F24" s="14">
         <v>2</v>
@@ -3507,14 +3991,14 @@
         <v>36</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -3522,31 +4006,31 @@
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="19" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T24" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>287</v>
       </c>
       <c r="U24" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V24" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W24" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X24" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y24" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z24" s="8" t="s">
-        <v>41</v>
+        <v>288</v>
       </c>
       <c r="AA24" s="8" t="s">
         <v>41</v>
@@ -3558,28 +4042,31 @@
         <v>41</v>
       </c>
       <c r="AD24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE24" s="8"/>
-      <c r="AF24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32" ht="57">
+      <c r="AF24" s="8"/>
+      <c r="AG24" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" ht="57">
       <c r="A25" s="8" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F25" s="14">
         <v>1</v>
@@ -3591,10 +4078,10 @@
         <v>36</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8" t="s">
@@ -3602,39 +4089,39 @@
       </c>
       <c r="M25" s="8"/>
       <c r="N25" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O25" s="8"/>
       <c r="P25" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="19" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T25" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U25" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="U25" s="19" t="s">
+        <v>290</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X25" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y25" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z25" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA25" s="8" t="s">
         <v>41</v>
@@ -3646,28 +4133,31 @@
         <v>41</v>
       </c>
       <c r="AD25" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE25" s="8"/>
-      <c r="AF25" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32" ht="57">
+      <c r="AF25" s="8"/>
+      <c r="AG25" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" ht="71.25">
       <c r="A26" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>164</v>
+        <v>155</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>291</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="F26" s="14">
         <v>1</v>
@@ -3679,52 +4169,52 @@
         <v>36</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>48</v>
       </c>
       <c r="M26" s="8"/>
       <c r="N26" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="Q26" s="8"/>
       <c r="R26" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="S26" s="8" t="s">
-        <v>41</v>
+        <v>243</v>
+      </c>
+      <c r="S26" s="19" t="s">
+        <v>286</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="U26" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="W26" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="X26" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y26" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z26" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="Y26" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z26" s="19" t="s">
+        <v>285</v>
       </c>
       <c r="AA26" s="8" t="s">
         <v>41</v>
@@ -3736,28 +4226,31 @@
         <v>41</v>
       </c>
       <c r="AD26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE26" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE26" s="8"/>
-      <c r="AF26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32" ht="57">
+      <c r="AF26" s="8"/>
+      <c r="AG26" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" ht="85.5">
       <c r="A27" s="8" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>168</v>
+        <v>292</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -3769,10 +4262,10 @@
         <v>36</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -3782,31 +4275,31 @@
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="19" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U27" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="T27" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="U27" s="19" t="s">
+        <v>293</v>
       </c>
       <c r="V27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W27" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
+      </c>
+      <c r="W27" s="19" t="s">
+        <v>295</v>
       </c>
       <c r="X27" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Y27" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Z27" s="8" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="AA27" s="8" t="s">
         <v>41</v>
@@ -3818,28 +4311,31 @@
         <v>41</v>
       </c>
       <c r="AD27" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE27" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AE27" s="8"/>
-      <c r="AF27" t="s">
-        <v>225</v>
+      <c r="AF27" s="8"/>
+      <c r="AG27" s="28" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
-  <conditionalFormatting sqref="AD2:AD27">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AD2="確認済み"</formula>
+  <conditionalFormatting sqref="AE2:AE27">
+    <cfRule type="expression" dxfId="16" priority="1">
+      <formula>AE2="確認済み"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AD2="一部入力済み"</formula>
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>AE2="一部入力済み"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>AD2="未入力"</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>AE2="未入力"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="AD2:AD27" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="AE2:AE27" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"未入力,入力中,一部入力済み,確認済み"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="F2:F27" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -3850,7 +4346,7 @@
       <formula1>18</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AF2:AF27" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" sqref="AG2:AG27" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"男性,女性,その他,非公表,未確認"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3881,10 +4377,48 @@
     <hyperlink ref="R25" r:id="rId24" xr:uid="{12E3B6CE-12B7-4FE1-B24F-DEED894670A6}"/>
     <hyperlink ref="R26" r:id="rId25" xr:uid="{061A4302-898B-44AE-9492-DE7D90017021}"/>
     <hyperlink ref="R27" r:id="rId26" xr:uid="{9470AA1D-CDA4-4AC1-AF43-012757E25450}"/>
+    <hyperlink ref="U2" r:id="rId27" xr:uid="{8C928C6C-DF24-4352-A49A-959D173510E3}"/>
+    <hyperlink ref="Y2" r:id="rId28" xr:uid="{C3DBA2A4-7AF4-4A8C-B5D4-BD41C2B07379}"/>
+    <hyperlink ref="U3" r:id="rId29" xr:uid="{76020712-73FC-4F9B-AACE-69C27E6D52AD}"/>
+    <hyperlink ref="T3" r:id="rId30" xr:uid="{9B6178C3-E3D7-425D-88B4-607E842A17F3}"/>
+    <hyperlink ref="T4" r:id="rId31" xr:uid="{F3629A8B-C78C-4898-B0A0-89585D705891}"/>
+    <hyperlink ref="T5" r:id="rId32" xr:uid="{F90E9F74-4CD1-4927-9948-B65F7CAE59F9}"/>
+    <hyperlink ref="T7" r:id="rId33" xr:uid="{02D2EA38-C631-4927-8F94-F6962215C462}"/>
+    <hyperlink ref="T8" r:id="rId34" xr:uid="{FE1C6007-D8CB-4B1E-8646-2E43894D86D3}"/>
+    <hyperlink ref="U9" r:id="rId35" xr:uid="{287CBAD8-400E-48F9-AEC6-80AC713FEF56}"/>
+    <hyperlink ref="T12" r:id="rId36" xr:uid="{21C80951-F8B1-4CA8-B0E8-2EA26D69B7B4}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{0E16E8FA-8E4D-4714-AF4F-ED32EDFDE4FD}"/>
+    <hyperlink ref="S13" r:id="rId38" xr:uid="{94DAE800-47D6-4904-AA40-1376F7EFC9A2}"/>
+    <hyperlink ref="T13" r:id="rId39" xr:uid="{DD0C7660-D665-4EB6-B37A-956A0FC21BC4}"/>
+    <hyperlink ref="T14" r:id="rId40" xr:uid="{B34F6605-8240-4349-9091-8C3661DE14D8}"/>
+    <hyperlink ref="X14" r:id="rId41" xr:uid="{97AAC1E3-B4B2-4E37-AD0E-F11AF80C4D19}"/>
+    <hyperlink ref="U15" r:id="rId42" xr:uid="{8EB7B6D1-A39D-4DAD-B4CD-CD2E676928AB}"/>
+    <hyperlink ref="V15" r:id="rId43" xr:uid="{65E61AD9-D037-4204-9A60-DAFFE00D81AD}"/>
+    <hyperlink ref="U16" r:id="rId44" xr:uid="{8EBD7592-0638-4B0E-A007-F327904F7F72}"/>
+    <hyperlink ref="T16" r:id="rId45" xr:uid="{C02D49BD-EB4D-4BF7-87A4-4A01247C57C3}"/>
+    <hyperlink ref="U19" r:id="rId46" xr:uid="{DF2D2C1E-4E14-4ABE-930A-EDF1258FF7E3}"/>
+    <hyperlink ref="T19" r:id="rId47" xr:uid="{834E03F8-57D2-4814-9F52-2253169A7B75}"/>
+    <hyperlink ref="U22" r:id="rId48" xr:uid="{66EA6CBF-5674-4C03-A3C5-9E9D5BF7E601}"/>
+    <hyperlink ref="W22" r:id="rId49" xr:uid="{D21779DD-195D-4E2E-9232-AF697FF827D9}"/>
+    <hyperlink ref="Z22" r:id="rId50" xr:uid="{C5094E3A-8ED0-4526-8D18-6C7263636537}"/>
+    <hyperlink ref="T22" r:id="rId51" xr:uid="{61A08795-F35C-481E-BCCC-621325712465}"/>
+    <hyperlink ref="S22" r:id="rId52" xr:uid="{DBF6EAEB-628E-4EFB-903C-AAB432AA6EDB}"/>
+    <hyperlink ref="Z14" r:id="rId53" xr:uid="{A3470F7D-7CEB-4A5E-83C7-C5125B897EF5}"/>
+    <hyperlink ref="Z5" r:id="rId54" xr:uid="{9AA63C41-AA94-46BB-93F9-9ACAEBCD9FC6}"/>
+    <hyperlink ref="Y5" r:id="rId55" xr:uid="{9D3F4F56-D711-412D-B0C5-EE0179404ED3}"/>
+    <hyperlink ref="Z26" r:id="rId56" xr:uid="{0857F1BA-0939-40A8-8510-76ACE5F5289A}"/>
+    <hyperlink ref="Y26" r:id="rId57" xr:uid="{15A25A7F-841A-4FC6-8DA3-350DF2264512}"/>
+    <hyperlink ref="S26" r:id="rId58" xr:uid="{27DFD8A6-2305-4A06-9F45-62E7C2527E17}"/>
+    <hyperlink ref="T24" r:id="rId59" xr:uid="{B9B39E8E-5618-47B5-8D14-5C1B0CFEA23B}"/>
+    <hyperlink ref="T25" r:id="rId60" xr:uid="{1E15584E-89F1-4DEB-A70B-C3F0EBABEE8F}"/>
+    <hyperlink ref="U25" r:id="rId61" xr:uid="{CDE3571C-DB27-4A4D-B413-24C1A5AAF690}"/>
+    <hyperlink ref="U27" r:id="rId62" xr:uid="{FF3375BC-7A4A-433B-851E-AC90B101927C}"/>
+    <hyperlink ref="T27" r:id="rId63" xr:uid="{EEA5401C-3E47-490C-8647-5FADDE5E93B2}"/>
+    <hyperlink ref="W27" r:id="rId64" xr:uid="{24E07791-96A5-45BB-B0CD-475BE3A1AAD1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId27"/>
+    <tablePart r:id="rId65"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3908,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>30</v>
@@ -3922,55 +4456,55 @@
         <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4000,7 +4534,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -4010,22 +4544,22 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4033,19 +4567,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4053,16 +4587,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -4071,16 +4605,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -4089,19 +4623,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4109,19 +4643,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4129,19 +4663,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4149,59 +4683,59 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.5">
@@ -4209,19 +4743,19 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4229,19 +4763,19 @@
         <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4249,22 +4783,22 @@
         <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="18" spans="1:6" ht="44.1" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -4274,22 +4808,22 @@
     </row>
     <row r="19" spans="1:6" ht="28.5">
       <c r="A19" s="16" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/議員データ.xlsx
+++ b/議員データ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/346989c40827ea06/ドキュメント/デスクトップ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\nobeoka-gikai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="13_ncr:1_{DBBC9D1B-790A-412B-8429-184B19BD81D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D7ED95-8C44-482E-BF4B-F7886C32F684}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC50ECB-D920-4EBC-8746-24BFA8C26429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,9 +299,6 @@
   </si>
   <si>
     <t>かい ただあつ</t>
-  </si>
-  <si>
-    <t>kai-tadaatu,jpg</t>
   </si>
   <si>
     <t>m08</t>
@@ -1330,6 +1327,10 @@
   </si>
   <si>
     <t>https://www.youtube.com/channel/UCbD24WObkKTQnPN3eI16b4g/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>kai-tadaatu.jpg</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1560,15 +1561,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1587,6 +1579,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1594,6 +1595,55 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF6B7280"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1633,55 +1683,6 @@
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF6B7280"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F4F6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1716,20 +1717,20 @@
     <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="所属委員会4"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="役職4"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="プロフィール"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="X" dataDxfId="7"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Facebook" dataDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Instagram" dataDxfId="5"/>
-    <tableColumn id="32" xr3:uid="{AE8A63C2-B2DC-4887-A3FE-6E6E373D5B77}" name="Threads" dataDxfId="4" dataCellStyle="Normal"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="YouTube" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="LINE" dataDxfId="2"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ブログ" dataDxfId="1"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ホームページ" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="X" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Facebook" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Instagram" dataDxfId="14"/>
+    <tableColumn id="32" xr3:uid="{AE8A63C2-B2DC-4887-A3FE-6E6E373D5B77}" name="Threads" dataDxfId="13" dataCellStyle="Normal"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="YouTube" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="LINE" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ブログ" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ホームページ" dataDxfId="9"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="一般質問" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="議案への賛否" dataDxfId="13"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="活動レポート" dataDxfId="12"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="情報源URL" dataDxfId="11"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="確認状況" dataDxfId="10"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="備考" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="議案への賛否" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="活動レポート" dataDxfId="6"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="情報源URL" dataDxfId="5"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="確認状況" dataDxfId="4"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="備考" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1920,7 +1921,7 @@
     <col min="19" max="19" width="11.625" style="7" customWidth="1"/>
     <col min="20" max="20" width="16.125" style="7" customWidth="1"/>
     <col min="21" max="25" width="11.625" style="7" customWidth="1"/>
-    <col min="26" max="26" width="14.75" style="29" customWidth="1"/>
+    <col min="26" max="26" width="14.75" style="26" customWidth="1"/>
     <col min="27" max="27" width="11.625" style="7" customWidth="1"/>
     <col min="28" max="29" width="14.75" style="7" customWidth="1"/>
     <col min="30" max="30" width="11.875" style="7" customWidth="1"/>
@@ -1995,7 +1996,7 @@
         <v>20</v>
       </c>
       <c r="V1" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W1" s="11" t="s">
         <v>21</v>
@@ -2028,7 +2029,7 @@
         <v>30</v>
       </c>
       <c r="AG1" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="57">
@@ -2074,31 +2075,31 @@
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
       <c r="R2" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U2" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y2" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="V2" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y2" s="19" t="s">
-        <v>246</v>
-      </c>
       <c r="Z2" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA2" s="8" t="s">
         <v>41</v>
@@ -2116,8 +2117,8 @@
         <v>42</v>
       </c>
       <c r="AF2" s="8"/>
-      <c r="AG2" s="28" t="s">
-        <v>215</v>
+      <c r="AG2" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="57">
@@ -2163,31 +2164,31 @@
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="T3" s="24" t="s">
-        <v>248</v>
+        <v>257</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>247</v>
       </c>
       <c r="U3" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>41</v>
@@ -2205,16 +2206,16 @@
         <v>42</v>
       </c>
       <c r="AF3" s="8"/>
-      <c r="AG3" s="28" t="s">
-        <v>215</v>
+      <c r="AG3" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="57">
       <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>249</v>
+      <c r="B4" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>50</v>
@@ -2252,31 +2253,31 @@
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T4" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA4" s="8" t="s">
         <v>41</v>
@@ -2294,8 +2295,8 @@
         <v>42</v>
       </c>
       <c r="AF4" s="8"/>
-      <c r="AG4" s="28" t="s">
-        <v>215</v>
+      <c r="AG4" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="57">
@@ -2337,31 +2338,31 @@
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y5" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Z5" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AA5" s="8" t="s">
         <v>41</v>
@@ -2379,8 +2380,8 @@
         <v>42</v>
       </c>
       <c r="AF5" s="8"/>
-      <c r="AG5" s="28" t="s">
-        <v>215</v>
+      <c r="AG5" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="57">
@@ -2426,31 +2427,31 @@
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA6" s="8" t="s">
         <v>41</v>
@@ -2468,16 +2469,16 @@
         <v>42</v>
       </c>
       <c r="AF6" s="8"/>
-      <c r="AG6" s="28" t="s">
-        <v>215</v>
+      <c r="AG6" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="57" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>252</v>
+      <c r="B7" s="23" t="s">
+        <v>251</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>70</v>
@@ -2519,31 +2520,31 @@
       </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T7" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X7" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA7" s="8" t="s">
         <v>41</v>
@@ -2561,16 +2562,16 @@
         <v>42</v>
       </c>
       <c r="AF7" s="8"/>
-      <c r="AG7" s="28" t="s">
-        <v>215</v>
+      <c r="AG7" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="57" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>254</v>
+      <c r="B8" s="22" t="s">
+        <v>253</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>76</v>
@@ -2591,7 +2592,7 @@
         <v>36</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>67</v>
@@ -2606,31 +2607,31 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T8" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA8" s="8" t="s">
         <v>41</v>
@@ -2648,19 +2649,19 @@
         <v>42</v>
       </c>
       <c r="AF8" s="8"/>
-      <c r="AG8" s="28" t="s">
-        <v>215</v>
+      <c r="AG8" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="57" customHeight="1">
       <c r="A9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>51</v>
@@ -2678,10 +2679,10 @@
         <v>36</v>
       </c>
       <c r="I9" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8" t="s">
@@ -2693,31 +2694,31 @@
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U9" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA9" s="8" t="s">
         <v>41</v>
@@ -2735,19 +2736,19 @@
         <v>42</v>
       </c>
       <c r="AF9" s="8"/>
-      <c r="AG9" s="28" t="s">
-        <v>215</v>
+      <c r="AG9" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="57">
       <c r="A10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>34</v>
@@ -2765,7 +2766,7 @@
         <v>36</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>61</v>
@@ -2786,31 +2787,31 @@
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
       <c r="R10" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V10" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W10" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="W10" s="8" t="s">
-        <v>259</v>
-      </c>
       <c r="X10" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y10" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AA10" s="8" t="s">
         <v>41</v>
@@ -2828,19 +2829,19 @@
         <v>42</v>
       </c>
       <c r="AF10" s="8"/>
-      <c r="AG10" s="28" t="s">
-        <v>215</v>
+      <c r="AG10" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="57">
       <c r="A11" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>51</v>
@@ -2858,7 +2859,7 @@
         <v>36</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>67</v>
@@ -2877,31 +2878,31 @@
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="U11" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V11" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W11" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="W11" s="8" t="s">
-        <v>259</v>
-      </c>
       <c r="X11" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y11" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z11" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AA11" s="8" t="s">
         <v>41</v>
@@ -2919,19 +2920,19 @@
         <v>42</v>
       </c>
       <c r="AF11" s="8"/>
-      <c r="AG11" s="28" t="s">
-        <v>215</v>
+      <c r="AG11" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="57">
       <c r="A12" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>34</v>
@@ -2949,7 +2950,7 @@
         <v>36</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>61</v>
@@ -2962,31 +2963,31 @@
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
       <c r="R12" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S12" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="T12" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="T12" s="19" t="s">
-        <v>260</v>
-      </c>
       <c r="U12" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V12" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W12" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="W12" s="8" t="s">
-        <v>259</v>
-      </c>
       <c r="X12" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y12" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z12" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AA12" s="8" t="s">
         <v>41</v>
@@ -3004,25 +3005,25 @@
         <v>42</v>
       </c>
       <c r="AF12" s="8"/>
-      <c r="AG12" s="28" t="s">
-        <v>215</v>
+      <c r="AG12" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="57">
       <c r="A13" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>97</v>
       </c>
       <c r="F13" s="14">
         <v>1</v>
@@ -3034,7 +3035,7 @@
         <v>36</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>67</v>
@@ -3047,31 +3048,31 @@
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
       <c r="R13" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S13" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="T13" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="T13" s="19" t="s">
-        <v>264</v>
-      </c>
       <c r="U13" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V13" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W13" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X13" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y13" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z13" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA13" s="8" t="s">
         <v>41</v>
@@ -3089,19 +3090,19 @@
         <v>42</v>
       </c>
       <c r="AF13" s="8"/>
-      <c r="AG13" s="28" t="s">
-        <v>215</v>
+      <c r="AG13" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="57">
       <c r="A14" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>71</v>
@@ -3119,14 +3120,14 @@
         <v>36</v>
       </c>
       <c r="I14" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M14" s="8" t="s">
         <v>54</v>
@@ -3136,31 +3137,31 @@
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
       <c r="R14" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S14" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T14" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W14" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="X14" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="U14" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="V14" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="W14" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="X14" s="19" t="s">
-        <v>267</v>
-      </c>
       <c r="Y14" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z14" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AA14" s="8" t="s">
         <v>41</v>
@@ -3178,19 +3179,19 @@
         <v>42</v>
       </c>
       <c r="AF14" s="8"/>
-      <c r="AG14" s="28" t="s">
-        <v>218</v>
+      <c r="AG14" s="25" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="57">
       <c r="A15" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>106</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>34</v>
@@ -3208,14 +3209,14 @@
         <v>36</v>
       </c>
       <c r="I15" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>40</v>
@@ -3225,31 +3226,31 @@
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S15" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="U15" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="V15" s="24" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="U15" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="V15" s="21" t="s">
+        <v>269</v>
       </c>
       <c r="W15" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X15" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z15" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA15" s="8" t="s">
         <v>41</v>
@@ -3267,19 +3268,19 @@
         <v>42</v>
       </c>
       <c r="AF15" s="8"/>
-      <c r="AG15" s="28" t="s">
-        <v>215</v>
+      <c r="AG15" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="57">
       <c r="A16" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>34</v>
@@ -3297,16 +3298,16 @@
         <v>36</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>67</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -3314,31 +3315,31 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S16" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T16" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="U16" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W16" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X16" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y16" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z16" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA16" s="8" t="s">
         <v>41</v>
@@ -3356,25 +3357,25 @@
         <v>42</v>
       </c>
       <c r="AF16" s="8"/>
-      <c r="AG16" s="28" t="s">
-        <v>215</v>
+      <c r="AG16" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="57">
       <c r="A17" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="D17" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>97</v>
       </c>
       <c r="F17" s="14">
         <v>6</v>
@@ -3386,10 +3387,10 @@
         <v>36</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -3399,31 +3400,31 @@
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
       <c r="R17" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA17" s="8" t="s">
         <v>41</v>
@@ -3441,25 +3442,25 @@
         <v>42</v>
       </c>
       <c r="AF17" s="8"/>
-      <c r="AG17" s="28" t="s">
-        <v>218</v>
+      <c r="AG17" s="25" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="57">
       <c r="A18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="F18" s="14">
         <v>4</v>
@@ -3471,14 +3472,14 @@
         <v>36</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>61</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
@@ -3486,31 +3487,31 @@
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA18" s="8" t="s">
         <v>41</v>
@@ -3528,19 +3529,19 @@
         <v>42</v>
       </c>
       <c r="AF18" s="8"/>
-      <c r="AG18" s="28" t="s">
-        <v>218</v>
+      <c r="AG18" s="25" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="57">
       <c r="A19" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>71</v>
@@ -3558,10 +3559,10 @@
         <v>36</v>
       </c>
       <c r="I19" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>127</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -3571,31 +3572,31 @@
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T19" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="U19" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA19" s="8" t="s">
         <v>41</v>
@@ -3613,19 +3614,19 @@
         <v>42</v>
       </c>
       <c r="AF19" s="8"/>
-      <c r="AG19" s="28" t="s">
-        <v>215</v>
+      <c r="AG19" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="57">
       <c r="A20" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>58</v>
@@ -3643,7 +3644,7 @@
         <v>36</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>67</v>
@@ -3658,31 +3659,31 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S20" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U20" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V20" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="X20" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y20" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z20" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA20" s="8" t="s">
         <v>41</v>
@@ -3700,25 +3701,25 @@
         <v>42</v>
       </c>
       <c r="AF20" s="8"/>
-      <c r="AG20" s="28" t="s">
-        <v>218</v>
+      <c r="AG20" s="25" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="57">
       <c r="A21" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="F21" s="14">
         <v>7</v>
@@ -3730,14 +3731,14 @@
         <v>36</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>61</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M21" s="8"/>
       <c r="N21" s="8" t="s">
@@ -3747,31 +3748,31 @@
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA21" s="8" t="s">
         <v>41</v>
@@ -3789,19 +3790,19 @@
         <v>42</v>
       </c>
       <c r="AF21" s="8"/>
-      <c r="AG21" s="28" t="s">
-        <v>215</v>
+      <c r="AG21" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="70.5" customHeight="1">
       <c r="A22" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>71</v>
@@ -3819,13 +3820,13 @@
         <v>36</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>61</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
@@ -3834,31 +3835,31 @@
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S22" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T22" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U22" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W22" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="V22" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="W22" s="19" t="s">
+      <c r="X22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z22" s="21" t="s">
         <v>278</v>
-      </c>
-      <c r="X22" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y22" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z22" s="24" t="s">
-        <v>279</v>
       </c>
       <c r="AA22" s="8" t="s">
         <v>41</v>
@@ -3876,19 +3877,19 @@
         <v>42</v>
       </c>
       <c r="AF22" s="8"/>
-      <c r="AG22" s="28" t="s">
-        <v>215</v>
+      <c r="AG22" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:33" ht="57">
       <c r="A23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>34</v>
@@ -3906,10 +3907,10 @@
         <v>36</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
@@ -3919,31 +3920,31 @@
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA23" s="8" t="s">
         <v>41</v>
@@ -3961,19 +3962,19 @@
         <v>42</v>
       </c>
       <c r="AF23" s="8"/>
-      <c r="AG23" s="28" t="s">
-        <v>215</v>
+      <c r="AG23" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:33" ht="85.5">
       <c r="A24" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>51</v>
@@ -3991,14 +3992,14 @@
         <v>36</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>67</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -4006,31 +4007,31 @@
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T24" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="V24" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W24" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="X24" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y24" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z24" s="8" t="s">
         <v>287</v>
-      </c>
-      <c r="U24" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="V24" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="W24" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="X24" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y24" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z24" s="8" t="s">
-        <v>288</v>
       </c>
       <c r="AA24" s="8" t="s">
         <v>41</v>
@@ -4048,25 +4049,25 @@
         <v>42</v>
       </c>
       <c r="AF24" s="8"/>
-      <c r="AG24" s="28" t="s">
-        <v>215</v>
+      <c r="AG24" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="57">
       <c r="A25" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>152</v>
-      </c>
       <c r="D25" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="F25" s="14">
         <v>1</v>
@@ -4078,7 +4079,7 @@
         <v>36</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>67</v>
@@ -4093,35 +4094,35 @@
       </c>
       <c r="O25" s="8"/>
       <c r="P25" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T25" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="U25" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="U25" s="19" t="s">
-        <v>290</v>
-      </c>
       <c r="V25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA25" s="8" t="s">
         <v>41</v>
@@ -4139,19 +4140,19 @@
         <v>42</v>
       </c>
       <c r="AF25" s="8"/>
-      <c r="AG25" s="28" t="s">
-        <v>215</v>
+      <c r="AG25" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="71.25">
       <c r="A26" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>58</v>
@@ -4169,52 +4170,52 @@
         <v>36</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>48</v>
       </c>
       <c r="M26" s="8"/>
       <c r="N26" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q26" s="8"/>
       <c r="R26" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="S26" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U26" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W26" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X26" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y26" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Z26" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA26" s="8" t="s">
         <v>41</v>
@@ -4232,19 +4233,19 @@
         <v>42</v>
       </c>
       <c r="AF26" s="8"/>
-      <c r="AG26" s="28" t="s">
-        <v>218</v>
+      <c r="AG26" s="25" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="85.5">
       <c r="A27" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>51</v>
@@ -4262,10 +4263,10 @@
         <v>36</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -4275,31 +4276,31 @@
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T27" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="U27" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="V27" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W27" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="U27" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="V27" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="W27" s="19" t="s">
-        <v>295</v>
-      </c>
       <c r="X27" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y27" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z27" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA27" s="8" t="s">
         <v>41</v>
@@ -4317,20 +4318,20 @@
         <v>42</v>
       </c>
       <c r="AF27" s="8"/>
-      <c r="AG27" s="28" t="s">
-        <v>215</v>
+      <c r="AG27" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
   <conditionalFormatting sqref="AE2:AE27">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>AE2="確認済み"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AE2="一部入力済み"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AE2="未入力"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4442,7 +4443,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>30</v>
@@ -4456,15 +4457,15 @@
         <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4472,7 +4473,7 @@
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4485,10 +4486,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4501,10 +4502,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4533,33 +4534,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="A1" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4567,19 +4568,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4587,16 +4588,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -4605,16 +4606,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -4623,19 +4624,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4643,19 +4644,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4663,19 +4664,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4683,59 +4684,59 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.5">
@@ -4743,19 +4744,19 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4763,19 +4764,19 @@
         <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4783,47 +4784,47 @@
         <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="18" spans="1:6" ht="44.1" customHeight="1">
+      <c r="A18" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="44.1" customHeight="1">
-      <c r="A18" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
     </row>
     <row r="19" spans="1:6" ht="28.5">
       <c r="A19" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="C19" s="17" t="s">
+      <c r="D19" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="F19" s="18" t="s">
         <v>216</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
